--- a/events/LaSeu_2015_WC/LaSeu_2015_WC_start.xlsx
+++ b/events/LaSeu_2015_WC/LaSeu_2015_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W651"/>
+  <dimension ref="A1:AC651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1388,7 @@
           <t>ZHANG Peng</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>63799</t>
         </is>
@@ -1416,7 +1446,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -1474,7 +1504,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -1518,7 +1548,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1532,6 +1562,11 @@
           <t>MERJAN Richard</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1585,7 +1620,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -1643,7 +1678,7 @@
           <t>KOLOMANSKI Michal</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35091</t>
         </is>
@@ -1701,7 +1736,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -1759,7 +1794,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -1817,7 +1852,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -1875,7 +1910,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -1933,7 +1968,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -1991,7 +2026,7 @@
           <t>SOETER Dennis</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>39166</t>
         </is>
@@ -2049,7 +2084,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -2107,7 +2142,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -2165,7 +2200,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -2223,7 +2258,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -2281,7 +2316,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -2339,7 +2374,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -2450,7 +2485,7 @@
           <t>NIEC Arkadiusz</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>35470</t>
         </is>
@@ -2508,7 +2543,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -2566,7 +2601,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -2624,7 +2659,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -2735,7 +2770,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -2846,7 +2881,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -2904,7 +2939,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -2962,7 +2997,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -3020,7 +3055,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -3078,7 +3113,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -3136,7 +3171,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -3194,7 +3229,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -3252,7 +3287,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -3310,7 +3345,7 @@
           <t>VIELLIARD Thibaud</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35588</t>
         </is>
@@ -3368,7 +3403,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -3426,7 +3461,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -3484,7 +3519,7 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -3542,7 +3577,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -3600,7 +3635,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -3658,7 +3693,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -3716,7 +3751,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -3774,7 +3809,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -3832,7 +3867,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -3890,7 +3925,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -3948,7 +3983,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -4006,7 +4041,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -4064,7 +4099,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -4122,7 +4157,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4180,7 +4215,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -4238,7 +4273,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4296,7 +4331,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -4354,7 +4389,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -4412,7 +4447,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -4470,7 +4505,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -4528,7 +4563,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -4586,7 +4621,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -4644,7 +4679,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -4702,7 +4737,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -4760,7 +4795,7 @@
           <t>JUETTNER Rebekka</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -4818,7 +4853,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -4929,7 +4964,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -5040,7 +5075,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -5151,7 +5186,7 @@
           <t>McGEE Alexandra</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>36261</t>
         </is>
@@ -5209,7 +5244,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -5267,7 +5302,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -5325,7 +5360,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -5383,7 +5418,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -5441,7 +5476,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -5499,7 +5534,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -5557,7 +5592,7 @@
           <t>WAGNER Karolin</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35176</t>
         </is>
@@ -5615,7 +5650,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -5726,7 +5761,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -5784,7 +5819,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -5842,7 +5877,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -5900,7 +5935,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -6011,7 +6046,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -6069,7 +6104,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6233,7 +6268,7 @@
           <t>NICHOLAS Bryden</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>36592</t>
         </is>
@@ -6291,7 +6326,7 @@
           <t>MAGALHAES Rodrigo</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>65983</t>
         </is>
@@ -6349,7 +6384,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -6407,7 +6442,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -6465,7 +6500,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -6523,7 +6558,7 @@
           <t>FLAGEUL Nathan, Gokul</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>60016</t>
         </is>
@@ -6581,7 +6616,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -6639,7 +6674,7 @@
           <t>ASAMI Meita</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>44316</t>
         </is>
@@ -6697,7 +6732,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -6755,7 +6790,7 @@
           <t>SONG Min Hyeong</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>42400</t>
         </is>
@@ -6813,7 +6848,7 @@
           <t>LEE Han-Cheng</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
@@ -6871,7 +6906,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -6929,7 +6964,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -6987,7 +7022,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -7045,7 +7080,7 @@
           <t>COLOBER Vivien</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35233</t>
         </is>
@@ -7103,7 +7138,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -7161,7 +7196,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -7219,7 +7254,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -7277,7 +7312,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -7335,7 +7370,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -7393,7 +7428,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -7451,7 +7486,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -7509,7 +7544,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -7620,7 +7655,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -7678,7 +7713,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -7736,7 +7771,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -7794,7 +7829,7 @@
           <t>CORDERO Matias</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
@@ -7852,7 +7887,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -7910,7 +7945,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -7968,7 +8003,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -8026,7 +8061,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -8084,7 +8119,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -8142,7 +8177,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -8200,7 +8235,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -8258,7 +8293,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -8316,7 +8351,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -8374,7 +8409,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -8432,7 +8467,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -8490,7 +8525,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -8548,7 +8583,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -8606,7 +8641,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -8664,7 +8699,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -8722,7 +8757,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -8833,7 +8868,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -8891,7 +8926,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -8949,7 +8984,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -9060,7 +9095,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -9118,7 +9153,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -9229,7 +9264,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -9287,7 +9322,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -9345,7 +9380,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -9403,7 +9438,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -9514,7 +9549,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -9625,7 +9660,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -9683,7 +9718,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -9741,7 +9776,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -9799,7 +9834,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -9857,7 +9892,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -9915,7 +9950,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -9973,7 +10008,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -10031,7 +10066,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -10089,7 +10124,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -10147,7 +10182,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -10205,7 +10240,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -10263,7 +10298,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -10321,7 +10356,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -10379,7 +10414,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -10437,7 +10472,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -10495,7 +10530,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -10553,7 +10588,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -10611,7 +10646,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -10669,7 +10704,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -10727,7 +10762,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -10785,7 +10820,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -10843,7 +10878,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -10901,7 +10936,7 @@
           <t>ZHANG Peng</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>63799</t>
         </is>
@@ -10959,7 +10994,7 @@
           <t>ZHANG Zhicheng</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>63800</t>
         </is>
@@ -11017,7 +11052,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -11061,7 +11096,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>LIB</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="J187" t="n">
@@ -11075,6 +11110,11 @@
           <t>MERJAN Richard</t>
         </is>
       </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>45918</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11128,7 +11168,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -11186,7 +11226,7 @@
           <t>KOLOMANSKI Michal</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35091</t>
         </is>
@@ -11244,7 +11284,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -11302,7 +11342,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -11360,7 +11400,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -11418,7 +11458,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -11476,7 +11516,7 @@
           <t>SOETER Dennis</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>39166</t>
         </is>
@@ -11534,7 +11574,7 @@
           <t>SMEDLEY Liam</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>36517</t>
         </is>
@@ -11592,7 +11632,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -11650,7 +11690,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -11708,7 +11748,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -11766,7 +11806,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -11824,7 +11864,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -11935,7 +11975,7 @@
           <t>NIEC Arkadiusz</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>35470</t>
         </is>
@@ -11993,7 +12033,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -12051,7 +12091,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -12109,7 +12149,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -12220,7 +12260,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -12278,7 +12318,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -12336,7 +12376,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -12394,7 +12434,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -12452,7 +12492,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -12510,7 +12550,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -12568,7 +12608,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -12626,7 +12666,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -12684,7 +12724,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -12742,7 +12782,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -12800,7 +12840,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -12858,7 +12898,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -12916,7 +12956,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -12974,7 +13014,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -13032,7 +13072,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -13090,7 +13130,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -13148,7 +13188,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -13206,7 +13246,7 @@
           <t>JUETTNER Rebekka</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -13264,7 +13304,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -13375,7 +13415,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -13486,7 +13526,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -13597,7 +13637,7 @@
           <t>McGEE Alexandra</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>36261</t>
         </is>
@@ -13655,7 +13695,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -13713,7 +13753,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -13771,7 +13811,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -13829,7 +13869,7 @@
           <t>NICHOLAS Bryden</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>36592</t>
         </is>
@@ -13887,7 +13927,7 @@
           <t>MAGALHAES Rodrigo</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>65983</t>
         </is>
@@ -13945,7 +13985,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -14003,7 +14043,7 @@
           <t>ZHAO Zhengchao</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>63802</t>
         </is>
@@ -14061,7 +14101,7 @@
           <t>ZHU Haoran</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>43553</t>
         </is>
@@ -14119,7 +14159,7 @@
           <t>FLAGEUL Nathan, Gokul</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>60016</t>
         </is>
@@ -14177,7 +14217,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -14235,7 +14275,7 @@
           <t>ASAMI Meita</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>44316</t>
         </is>
@@ -14293,7 +14333,7 @@
           <t>HENGST Stefan</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>39061</t>
         </is>
@@ -14351,7 +14391,7 @@
           <t>SONG Min Hyeong</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>42400</t>
         </is>
@@ -14409,7 +14449,7 @@
           <t>LEE Han-Cheng</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>39369</t>
         </is>
@@ -14467,7 +14507,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -14525,7 +14565,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -14583,7 +14623,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -14641,7 +14681,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -14699,7 +14739,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -14757,7 +14797,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -14815,7 +14855,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -14873,7 +14913,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -14931,7 +14971,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -14989,7 +15029,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -15100,7 +15140,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -15158,7 +15198,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -15216,7 +15256,7 @@
           <t>NABASKUES Unai</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>38775</t>
         </is>
@@ -15274,7 +15314,7 @@
           <t>CORDERO Matias</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>36918</t>
         </is>
@@ -15332,7 +15372,7 @@
           <t>RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -15390,7 +15430,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -15448,7 +15488,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -15506,7 +15546,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -15564,7 +15604,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -15622,7 +15662,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -15680,7 +15720,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -15738,7 +15778,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -15796,7 +15836,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -15854,7 +15894,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -15912,7 +15952,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -15970,7 +16010,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -16028,7 +16068,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -16086,7 +16126,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -16144,7 +16184,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -16202,7 +16242,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -16313,7 +16353,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -16371,7 +16411,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -16535,7 +16575,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -16593,7 +16633,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -16651,7 +16691,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -16709,7 +16749,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -17032,7 +17072,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -17143,7 +17183,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -17201,7 +17241,7 @@
           <t>KAIFUCHI Moe</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>36483</t>
         </is>
@@ -17259,7 +17299,7 @@
           <t>BARANAUSKAITE Erika</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35622</t>
         </is>
@@ -17317,7 +17357,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -17428,7 +17468,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -17486,7 +17526,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -17544,7 +17584,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -17655,7 +17695,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -17713,7 +17753,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -17771,7 +17811,7 @@
           <t>ZASTEROVA Pavlina</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35051</t>
         </is>
@@ -17829,7 +17869,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -17887,7 +17927,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -17945,7 +17985,7 @@
           <t>PASTOR ROVIRA Zoe</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>43378</t>
         </is>
@@ -18003,7 +18043,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -18061,7 +18101,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -18119,7 +18159,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -18230,7 +18270,7 @@
           <t>FEREKIDOU Maria</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35434</t>
         </is>
@@ -18288,7 +18328,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -18346,7 +18386,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -18404,7 +18444,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -18515,7 +18555,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -18573,7 +18613,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -18631,7 +18671,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -18689,7 +18729,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -18853,7 +18893,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -18911,7 +18951,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -18969,7 +19009,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -19027,7 +19067,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -19085,7 +19125,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -19143,7 +19183,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -19201,7 +19241,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -19259,7 +19299,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -19317,7 +19357,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -19375,7 +19415,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -19433,7 +19473,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -19491,7 +19531,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -19549,7 +19589,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -19607,7 +19647,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -19665,7 +19705,7 @@
           <t>NEWMAN Nouria</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35397</t>
         </is>
@@ -19723,7 +19763,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -19781,7 +19821,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -19839,7 +19879,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -19897,7 +19937,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -19955,7 +19995,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -20013,7 +20053,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -20071,7 +20111,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -20129,7 +20169,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -20187,7 +20227,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -20245,7 +20285,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -20361,12 +20401,12 @@
           <t>SOMMER Paul</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>62836</t>
         </is>
       </c>
-      <c r="V349" t="inlineStr">
+      <c r="Y349" t="inlineStr">
         <is>
           <t>39162</t>
         </is>
@@ -20487,12 +20527,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V351" t="inlineStr">
+      <c r="Y351" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -20555,12 +20595,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V352" t="inlineStr">
+      <c r="Y352" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -20623,12 +20663,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V353" t="inlineStr">
+      <c r="Y353" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -20691,12 +20731,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V354" t="inlineStr">
+      <c r="Y354" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -20759,12 +20799,12 @@
           <t>WAGNER Piet Lennart</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>39063</t>
         </is>
       </c>
-      <c r="V355" t="inlineStr">
+      <c r="Y355" t="inlineStr">
         <is>
           <t>39180</t>
         </is>
@@ -20827,12 +20867,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V356" t="inlineStr">
+      <c r="Y356" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -20895,12 +20935,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V357" t="inlineStr">
+      <c r="Y357" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -20963,12 +21003,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V358" t="inlineStr">
+      <c r="Y358" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -21031,12 +21071,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V359" t="inlineStr">
+      <c r="Y359" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -21099,7 +21139,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -21162,12 +21202,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V361" t="inlineStr">
+      <c r="Y361" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -21230,12 +21270,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V362" t="inlineStr">
+      <c r="Y362" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -21298,12 +21338,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V363" t="inlineStr">
+      <c r="Y363" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -21366,12 +21406,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V364" t="inlineStr">
+      <c r="Y364" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -21434,12 +21474,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V365" t="inlineStr">
+      <c r="Y365" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -21502,12 +21542,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V366" t="inlineStr">
+      <c r="Y366" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -21570,12 +21610,12 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35351</t>
         </is>
       </c>
-      <c r="V367" t="inlineStr">
+      <c r="Y367" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -21638,12 +21678,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V368" t="inlineStr">
+      <c r="Y368" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -21706,12 +21746,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V369" t="inlineStr">
+      <c r="Y369" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -21774,12 +21814,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V370" t="inlineStr">
+      <c r="Y370" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -21842,12 +21882,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V371" t="inlineStr">
+      <c r="Y371" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -21910,7 +21950,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -21973,12 +22013,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V373" t="inlineStr">
+      <c r="Y373" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -22041,12 +22081,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V374" t="inlineStr">
+      <c r="Y374" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -22109,12 +22149,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V375" t="inlineStr">
+      <c r="Y375" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -22177,12 +22217,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V376" t="inlineStr">
+      <c r="Y376" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -22293,7 +22333,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -22404,7 +22444,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -22462,7 +22502,7 @@
           <t>KAIFUCHI Moe</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>36483</t>
         </is>
@@ -22520,7 +22560,7 @@
           <t>BARANAUSKAITE Erika</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35622</t>
         </is>
@@ -22578,7 +22618,7 @@
           <t>JAMILI Hind</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>43390</t>
         </is>
@@ -22636,7 +22676,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -22694,7 +22734,7 @@
           <t>OKAZAKI Haruka</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>42265</t>
         </is>
@@ -22752,7 +22792,7 @@
           <t>MISHIMA Ren</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>37757</t>
         </is>
@@ -22863,7 +22903,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -22921,7 +22961,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -22979,7 +23019,7 @@
           <t>ZASTEROVA Pavlina</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35051</t>
         </is>
@@ -23037,7 +23077,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -23095,7 +23135,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -23153,7 +23193,7 @@
           <t>PASTOR ROVIRA Zoe</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>43378</t>
         </is>
@@ -23211,7 +23251,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -23269,7 +23309,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -23327,7 +23367,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -23438,7 +23478,7 @@
           <t>FEREKIDOU Maria</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35434</t>
         </is>
@@ -23496,7 +23536,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -23554,7 +23594,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -23612,7 +23652,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -23723,7 +23763,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -23781,7 +23821,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -23839,7 +23879,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -23897,7 +23937,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -24061,7 +24101,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -24119,7 +24159,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -24177,7 +24217,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -24235,7 +24275,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -24293,7 +24333,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -24351,7 +24391,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -24409,7 +24449,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -24467,7 +24507,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -24530,12 +24570,12 @@
           <t>SOMMER Paul</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>62836</t>
         </is>
       </c>
-      <c r="V417" t="inlineStr">
+      <c r="Y417" t="inlineStr">
         <is>
           <t>39162</t>
         </is>
@@ -24598,12 +24638,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V418" t="inlineStr">
+      <c r="Y418" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -24666,12 +24706,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V419" t="inlineStr">
+      <c r="Y419" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -24734,12 +24774,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V420" t="inlineStr">
+      <c r="Y420" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -24802,12 +24842,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V421" t="inlineStr">
+      <c r="Y421" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -24870,12 +24910,12 @@
           <t>WAGNER Piet Lennart</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>39063</t>
         </is>
       </c>
-      <c r="V422" t="inlineStr">
+      <c r="Y422" t="inlineStr">
         <is>
           <t>39180</t>
         </is>
@@ -24938,12 +24978,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V423" t="inlineStr">
+      <c r="Y423" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -25006,12 +25046,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V424" t="inlineStr">
+      <c r="Y424" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -25074,7 +25114,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -25137,12 +25177,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V426" t="inlineStr">
+      <c r="Y426" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -25205,12 +25245,12 @@
           <t>LARIONOV Dmitry</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35449</t>
         </is>
       </c>
-      <c r="V427" t="inlineStr">
+      <c r="Y427" t="inlineStr">
         <is>
           <t>35450</t>
         </is>
@@ -25273,12 +25313,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V428" t="inlineStr">
+      <c r="Y428" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -25341,12 +25381,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V429" t="inlineStr">
+      <c r="Y429" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -25717,7 +25757,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -25775,7 +25815,7 @@
           <t>PFEIFFER Frederick</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>39878</t>
         </is>
@@ -25833,7 +25873,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -25891,7 +25931,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -25949,7 +25989,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -26007,7 +26047,7 @@
           <t>ERGUIN Jon</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>35740</t>
         </is>
@@ -26065,7 +26105,7 @@
           <t>LIPATOV Aleksandr</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35451</t>
         </is>
@@ -26123,7 +26163,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -26181,7 +26221,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -26239,7 +26279,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -26297,7 +26337,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -26355,7 +26395,7 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -26413,7 +26453,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -26471,7 +26511,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -26529,7 +26569,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -26587,7 +26627,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -26645,7 +26685,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -26703,7 +26743,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -26761,7 +26801,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -26819,7 +26859,7 @@
           <t>VIELLIARD Thibaud</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35588</t>
         </is>
@@ -26877,7 +26917,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -26988,7 +27028,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -27046,7 +27086,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -27104,7 +27144,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -27162,7 +27202,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -27220,7 +27260,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -27278,7 +27318,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -27336,7 +27376,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -27394,7 +27434,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -27452,7 +27492,7 @@
           <t>JUETTNER Rebekka</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -27510,7 +27550,7 @@
           <t>MATULKOVA Jana</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>37274</t>
         </is>
@@ -27621,7 +27661,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -27679,7 +27719,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -27737,7 +27777,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -27795,7 +27835,7 @@
           <t>WAGNER Karolin</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35176</t>
         </is>
@@ -27853,7 +27893,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -27964,7 +28004,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -28022,7 +28062,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -28080,7 +28120,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -28191,7 +28231,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -28249,7 +28289,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -28307,7 +28347,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -28418,7 +28458,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -28529,7 +28569,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -28587,7 +28627,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -28645,7 +28685,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -28703,7 +28743,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -28761,7 +28801,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -28819,7 +28859,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -28930,7 +28970,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -28988,7 +29028,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -29099,7 +29139,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -29157,7 +29197,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -29215,7 +29255,7 @@
           <t>PASIUT Michal</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35095</t>
         </is>
@@ -29273,7 +29313,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -29331,7 +29371,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -29389,7 +29429,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -29447,7 +29487,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -29505,7 +29545,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -29563,7 +29603,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -29727,7 +29767,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -29785,7 +29825,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -29843,7 +29883,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -29901,7 +29941,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -29959,7 +29999,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -30017,7 +30057,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -30075,7 +30115,7 @@
           <t>BOECKELMANN Paul</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35118</t>
         </is>
@@ -30133,7 +30173,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -30191,7 +30231,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -30249,7 +30289,7 @@
           <t>COLOBER Vivien</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35233</t>
         </is>
@@ -30307,7 +30347,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -30365,7 +30405,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -30423,7 +30463,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -30481,7 +30521,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -30539,7 +30579,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -30597,7 +30637,7 @@
           <t>KURT Michael</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35346</t>
         </is>
@@ -30655,7 +30695,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -30713,7 +30753,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -30771,7 +30811,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -30829,7 +30869,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -31205,7 +31245,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -31273,7 +31313,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -31341,7 +31381,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -31409,7 +31449,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -31477,7 +31517,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -31545,7 +31585,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -31613,7 +31653,7 @@
           <t>DOMENJO Jordi</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35739</t>
         </is>
@@ -31681,7 +31721,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -31749,7 +31789,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -31817,7 +31857,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -31885,7 +31925,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -31953,7 +31993,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -32147,7 +32187,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -32215,7 +32255,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -32283,7 +32323,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -32477,7 +32517,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -32545,7 +32585,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -32613,7 +32653,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -32681,7 +32721,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -32749,7 +32789,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -32817,7 +32857,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -32885,7 +32925,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -32943,7 +32983,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -33011,7 +33051,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -33079,7 +33119,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -33147,7 +33187,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -33978,7 +34018,7 @@
           <t>KAIFUCHI Moe</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>36483</t>
         </is>
@@ -34036,7 +34076,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -34094,7 +34134,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -34152,7 +34192,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -34210,7 +34250,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -34268,7 +34308,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -34326,7 +34366,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -34384,7 +34424,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -34495,7 +34535,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -34553,7 +34593,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -34611,7 +34651,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -34669,7 +34709,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -34727,7 +34767,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -34838,7 +34878,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -34896,7 +34936,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -34954,7 +34994,7 @@
           <t>NEWMAN Nouria</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35397</t>
         </is>
@@ -35012,7 +35052,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -35070,7 +35110,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -35128,7 +35168,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -35186,7 +35226,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -35244,7 +35284,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -35302,7 +35342,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -35360,7 +35400,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -35418,7 +35458,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -35529,7 +35569,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -35587,7 +35627,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -35645,7 +35685,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -35708,12 +35748,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V608" t="inlineStr">
+      <c r="Y608" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -35776,12 +35816,12 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35770</t>
         </is>
       </c>
-      <c r="V609" t="inlineStr">
+      <c r="Y609" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -35844,12 +35884,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V610" t="inlineStr">
+      <c r="Y610" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -35912,12 +35952,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V611" t="inlineStr">
+      <c r="Y611" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -35980,12 +36020,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V612" t="inlineStr">
+      <c r="Y612" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -36048,12 +36088,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V613" t="inlineStr">
+      <c r="Y613" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -36116,12 +36156,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V614" t="inlineStr">
+      <c r="Y614" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -36242,12 +36282,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V616" t="inlineStr">
+      <c r="Y616" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -36310,12 +36350,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V617" t="inlineStr">
+      <c r="Y617" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -36378,12 +36418,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V618" t="inlineStr">
+      <c r="Y618" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -36446,7 +36486,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -36509,12 +36549,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V620" t="inlineStr">
+      <c r="Y620" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -36577,12 +36617,12 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35351</t>
         </is>
       </c>
-      <c r="V621" t="inlineStr">
+      <c r="Y621" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -36645,12 +36685,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V622" t="inlineStr">
+      <c r="Y622" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -36713,12 +36753,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V623" t="inlineStr">
+      <c r="Y623" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -36781,12 +36821,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V624" t="inlineStr">
+      <c r="Y624" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -36849,12 +36889,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V625" t="inlineStr">
+      <c r="Y625" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -36917,12 +36957,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V626" t="inlineStr">
+      <c r="Y626" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -36985,12 +37025,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V627" t="inlineStr">
+      <c r="Y627" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -37270,7 +37310,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -37338,7 +37378,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -37406,7 +37446,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -37537,7 +37577,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -37605,7 +37645,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -37673,7 +37713,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -37741,7 +37781,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -37809,7 +37849,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U640" t="inlineStr">
+      <c r="X640" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -37877,7 +37917,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -37950,12 +37990,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V642" t="inlineStr">
+      <c r="Y642" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -38028,12 +38068,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V643" t="inlineStr">
+      <c r="Y643" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -38106,12 +38146,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V644" t="inlineStr">
+      <c r="Y644" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -38184,12 +38224,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U645" t="inlineStr">
+      <c r="X645" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V645" t="inlineStr">
+      <c r="Y645" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -38262,12 +38302,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V646" t="inlineStr">
+      <c r="Y646" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -38340,12 +38380,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V647" t="inlineStr">
+      <c r="Y647" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -38418,12 +38458,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V648" t="inlineStr">
+      <c r="Y648" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -38496,12 +38536,12 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35351</t>
         </is>
       </c>
-      <c r="V649" t="inlineStr">
+      <c r="Y649" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -38574,12 +38614,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V650" t="inlineStr">
+      <c r="Y650" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -38652,7 +38692,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
